--- a/payment_forms/034_domain_leasing_application_form--payment_forms.xlsx
+++ b/payment_forms/034_domain_leasing_application_form--payment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -746,7 +746,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -825,17 +825,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>domain_leasing_application_form_1_choices</t>
+          <t>business_use_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>lease_domain_name</t>
+          <t>business</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Lease Domain Name</t>
+          <t>Business</t>
         </is>
       </c>
     </row>
@@ -847,29 +847,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>business</t>
+          <t>personal</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Personal</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>business_use_choices</t>
+          <t>lease_duration_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>personal</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Personal</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -881,12 +881,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -898,29 +898,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>lease_duration_choices</t>
+          <t>website_maintenance_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -932,12 +932,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -949,29 +949,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>website_maintenance_choices</t>
+          <t>agreement_signing_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>by_hand</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>By Hand</t>
         </is>
       </c>
     </row>
@@ -983,12 +983,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>by_hand</t>
+          <t>online</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>By Hand</t>
+          <t>Online</t>
         </is>
       </c>
     </row>
@@ -1000,27 +1000,10 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>online</t>
+          <t>paper</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
-        <is>
-          <t>Online</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>agreement_signing_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>paper</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
         <is>
           <t>Paper</t>
         </is>
